--- a/resultados/saojoao/inventario_links.xlsx
+++ b/resultados/saojoao/inventario_links.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,6 +783,178 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>saojoao</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://www.portaltransparenciasaojoao.com.br/_files/ugd/cb1b73_fd74f0e4c47343b18dff4fc1fbec638e.pdf</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>www.portaltransparenciasaojoao.com.br</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>002/2017</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://www.portaltransparenciasaojoao.com.br/about-3</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>200</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-08-18 02:39:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>saojoao</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>https://www.portaltransparenciasaojoao.com.br/_files/ugd/cb1b73_2328d13b06ef4b0fbf2cbdaecd0acab7.pdf</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>www.portaltransparenciasaojoao.com.br</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>007/2018</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://www.portaltransparenciasaojoao.com.br/about-3</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>200</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-08-18 02:39:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>saojoao</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>https://www.portaltransparenciasaojoao.com.br/_files/ugd/cb1b73_ac7ecf8cdebd49e59afa80b58737fc1c.pdf</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>www.portaltransparenciasaojoao.com.br</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>002/2019</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://www.portaltransparenciasaojoao.com.br/about-3</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>.pdf</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>200</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-08-18 02:39:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>saojoao</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://www.portaltransparenciasaojoao.com.br/_files/ugd/cb1b73_ccc4a17535d6482ea0c7c3aca821b162.docx?dn=ficha%20de%20cadastro-2.docx</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>www.portaltransparenciasaojoao.com.br</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Ficha de cadastramento/recadastramento e solicitação de matrícula preenchida e assinada;</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://www.portaltransparenciasaojoao.com.br/about-3</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>.docx</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>200</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-08-18 02:39:09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
